--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
@@ -1076,7 +1076,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e9f5c328-2e87-4561-8ac7-909f5386c885}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a7fc5c19-fb83-434f-ae06-457e832997bd}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
@@ -324,11 +324,11 @@
           <c:bubble3D val="1"/>
         </c:ser>
         <c:showNegBubbles val="0"/>
-        <c:axId val="887840001"/>
-        <c:axId val="2008165125"/>
+        <c:axId val="241456640"/>
+        <c:axId val="242957908"/>
       </c:bubbleChart>
       <c:valAx>
-        <c:axId val="887840001"/>
+        <c:axId val="241456640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -385,12 +385,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2008165125"/>
+        <c:crossAx val="242957908"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2008165125"/>
+        <c:axId val="242957908"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -447,7 +447,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="887840001"/>
+        <c:crossAx val="241456640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1076,7 +1076,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{a7fc5c19-fb83-434f-ae06-457e832997bd}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f10c3075-9ea7-4390-8e7d-a71461a2c3fe}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Bubble Chart_report.xlsx
@@ -324,11 +324,11 @@
           <c:bubble3D val="1"/>
         </c:ser>
         <c:showNegBubbles val="0"/>
-        <c:axId val="241456640"/>
-        <c:axId val="242957908"/>
+        <c:axId val="1291752852"/>
+        <c:axId val="1619402333"/>
       </c:bubbleChart>
       <c:valAx>
-        <c:axId val="241456640"/>
+        <c:axId val="1291752852"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -385,12 +385,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="242957908"/>
+        <c:crossAx val="1619402333"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="242957908"/>
+        <c:axId val="1619402333"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -447,7 +447,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="241456640"/>
+        <c:crossAx val="1291752852"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1076,7 +1076,7 @@
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{f10c3075-9ea7-4390-8e7d-a71461a2c3fe}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73e524b0-6c54-485d-aa8e-078994845e8e}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
